--- a/Action/Data/CSV/Stage/Platform.xlsx
+++ b/Action/Data/CSV/Stage/Platform.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action - コピー\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1C7883-86BD-45EF-925A-7B9004E8D800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C208232-351B-4777-949B-0D6BF3716033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -872,27 +872,27 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
